--- a/nr-update-system-nss/ig/CodeSystem-fr-core-cs-discipline-prestation.xlsx
+++ b/nr-update-system-nss/ig/CodeSystem-fr-core-cs-discipline-prestation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-system-nss/ig/CodeSystem-fr-core-cs-discipline-prestation.xlsx
+++ b/nr-update-system-nss/ig/CodeSystem-fr-core-cs-discipline-prestation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="557">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot-2</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:28:50+00:00</t>
+    <t>2026-03-25T14:42:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2028,7 +2028,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -2040,7 +2042,9 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -2052,7 +2056,9 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -2064,7 +2070,9 @@
       <c r="C5" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -2076,7 +2084,9 @@
       <c r="C6" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -2088,7 +2098,9 @@
       <c r="C7" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -2100,7 +2112,9 @@
       <c r="C8" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -2112,7 +2126,9 @@
       <c r="C9" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -2124,7 +2140,9 @@
       <c r="C10" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -2136,7 +2154,9 @@
       <c r="C11" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>62</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -2148,7 +2168,9 @@
       <c r="C12" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>64</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -2160,7 +2182,9 @@
       <c r="C13" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>66</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -2172,7 +2196,9 @@
       <c r="C14" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>68</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -2184,7 +2210,9 @@
       <c r="C15" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>70</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -2196,7 +2224,9 @@
       <c r="C16" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>72</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -2208,7 +2238,9 @@
       <c r="C17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>74</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
@@ -2220,7 +2252,9 @@
       <c r="C18" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>76</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
@@ -2232,7 +2266,9 @@
       <c r="C19" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
@@ -2244,7 +2280,9 @@
       <c r="C20" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>80</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
@@ -2256,7 +2294,9 @@
       <c r="C21" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>82</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
@@ -2268,7 +2308,9 @@
       <c r="C22" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>84</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
@@ -2280,7 +2322,9 @@
       <c r="C23" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="D23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>86</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
@@ -2292,7 +2336,9 @@
       <c r="C24" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="D24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>88</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
@@ -2304,7 +2350,9 @@
       <c r="C25" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="D25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>90</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
@@ -2316,7 +2364,9 @@
       <c r="C26" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="D26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>92</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
@@ -2328,7 +2378,9 @@
       <c r="C27" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="D27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>94</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
@@ -2340,7 +2392,9 @@
       <c r="C28" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="D28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>96</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
@@ -2352,7 +2406,9 @@
       <c r="C29" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="D29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>98</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
@@ -2364,7 +2420,9 @@
       <c r="C30" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="D30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>100</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
@@ -2376,7 +2434,9 @@
       <c r="C31" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="D31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>102</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
@@ -2388,7 +2448,9 @@
       <c r="C32" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="D32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>104</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
@@ -2400,7 +2462,9 @@
       <c r="C33" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="D33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>106</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
@@ -2412,7 +2476,9 @@
       <c r="C34" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="D34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>108</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
@@ -2424,7 +2490,9 @@
       <c r="C35" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="D35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>110</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
@@ -2436,7 +2504,9 @@
       <c r="C36" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="D36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>112</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
@@ -2448,7 +2518,9 @@
       <c r="C37" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="D37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>114</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
@@ -2460,7 +2532,9 @@
       <c r="C38" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="D38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>116</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
@@ -2472,7 +2546,9 @@
       <c r="C39" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="D39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>118</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
@@ -2484,7 +2560,9 @@
       <c r="C40" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="D40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>120</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
@@ -2496,7 +2574,9 @@
       <c r="C41" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="D41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>122</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
@@ -2508,7 +2588,9 @@
       <c r="C42" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="D42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>124</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
@@ -2520,7 +2602,9 @@
       <c r="C43" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="D43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>126</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
@@ -2532,7 +2616,9 @@
       <c r="C44" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="D44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>128</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
@@ -2544,7 +2630,9 @@
       <c r="C45" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="D45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>130</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
@@ -2556,7 +2644,9 @@
       <c r="C46" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="D46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>132</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
@@ -2568,7 +2658,9 @@
       <c r="C47" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="D47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>134</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
@@ -2580,7 +2672,9 @@
       <c r="C48" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="D48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>136</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
@@ -2592,7 +2686,9 @@
       <c r="C49" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="D49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>138</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
@@ -2604,7 +2700,9 @@
       <c r="C50" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="D50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>140</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
@@ -2616,7 +2714,9 @@
       <c r="C51" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="D51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>142</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
@@ -2628,7 +2728,9 @@
       <c r="C52" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="D52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>144</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
@@ -2640,7 +2742,9 @@
       <c r="C53" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="D53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>146</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
@@ -2652,7 +2756,9 @@
       <c r="C54" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="D54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>148</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
@@ -2664,7 +2770,9 @@
       <c r="C55" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="D55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>150</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
@@ -2676,7 +2784,9 @@
       <c r="C56" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="D56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>152</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
@@ -2688,7 +2798,9 @@
       <c r="C57" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="D57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>154</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
@@ -2700,7 +2812,9 @@
       <c r="C58" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="D58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>156</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
@@ -2712,7 +2826,9 @@
       <c r="C59" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="D59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>158</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
@@ -2724,7 +2840,9 @@
       <c r="C60" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="D60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>160</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
@@ -2736,7 +2854,9 @@
       <c r="C61" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="D61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>162</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
@@ -2748,7 +2868,9 @@
       <c r="C62" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="D62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>164</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
@@ -2760,7 +2882,9 @@
       <c r="C63" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="D63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>166</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
@@ -2772,7 +2896,9 @@
       <c r="C64" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="D64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>168</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
@@ -2784,7 +2910,9 @@
       <c r="C65" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="D65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>170</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
@@ -2796,7 +2924,9 @@
       <c r="C66" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="D66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>172</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
@@ -2808,7 +2938,9 @@
       <c r="C67" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="D67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>174</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
@@ -2820,7 +2952,9 @@
       <c r="C68" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="D68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>176</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
@@ -2832,7 +2966,9 @@
       <c r="C69" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="D69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>178</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
@@ -2844,7 +2980,9 @@
       <c r="C70" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="D70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>180</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
@@ -2856,7 +2994,9 @@
       <c r="C71" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="D71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>182</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
@@ -2868,7 +3008,9 @@
       <c r="C72" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="D72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>184</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
@@ -2880,7 +3022,9 @@
       <c r="C73" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="D73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>186</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
@@ -2892,7 +3036,9 @@
       <c r="C74" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="D74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>188</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
@@ -2904,7 +3050,9 @@
       <c r="C75" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="D75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>190</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
@@ -2916,7 +3064,9 @@
       <c r="C76" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="D76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>192</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
@@ -2928,7 +3078,9 @@
       <c r="C77" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="D77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>194</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
@@ -2940,7 +3092,9 @@
       <c r="C78" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="D78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>196</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
@@ -2952,7 +3106,9 @@
       <c r="C79" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="D79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>198</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
@@ -2964,7 +3120,9 @@
       <c r="C80" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="D80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>200</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
@@ -2976,7 +3134,9 @@
       <c r="C81" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="D81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>202</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
@@ -2988,7 +3148,9 @@
       <c r="C82" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="D82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>204</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
@@ -3000,7 +3162,9 @@
       <c r="C83" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="D83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>206</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
@@ -3012,7 +3176,9 @@
       <c r="C84" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="D84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>208</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
@@ -3024,7 +3190,9 @@
       <c r="C85" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="D85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>210</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
@@ -3036,7 +3204,9 @@
       <c r="C86" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="D86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>212</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
@@ -3048,7 +3218,9 @@
       <c r="C87" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="D87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>214</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
@@ -3060,7 +3232,9 @@
       <c r="C88" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="D88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>216</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
@@ -3072,7 +3246,9 @@
       <c r="C89" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="D89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>218</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
@@ -3084,7 +3260,9 @@
       <c r="C90" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="D90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>220</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
@@ -3096,7 +3274,9 @@
       <c r="C91" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="D91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>222</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
@@ -3108,7 +3288,9 @@
       <c r="C92" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="D92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>224</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
@@ -3120,7 +3302,9 @@
       <c r="C93" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="D93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>226</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
@@ -3132,7 +3316,9 @@
       <c r="C94" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="D94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>228</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
@@ -3144,7 +3330,9 @@
       <c r="C95" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="D95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>230</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
@@ -3156,7 +3344,9 @@
       <c r="C96" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="D96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>232</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
@@ -3168,7 +3358,9 @@
       <c r="C97" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="D97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>234</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
@@ -3180,7 +3372,9 @@
       <c r="C98" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="D98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>236</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
@@ -3192,7 +3386,9 @@
       <c r="C99" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="D99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>238</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
@@ -3204,7 +3400,9 @@
       <c r="C100" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="D100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>240</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
@@ -3216,7 +3414,9 @@
       <c r="C101" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="D101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>242</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
@@ -3228,7 +3428,9 @@
       <c r="C102" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="D102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>244</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
@@ -3240,7 +3442,9 @@
       <c r="C103" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="D103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>246</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
@@ -3252,7 +3456,9 @@
       <c r="C104" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="D104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>248</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
@@ -3264,7 +3470,9 @@
       <c r="C105" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="D105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>250</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
@@ -3276,7 +3484,9 @@
       <c r="C106" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="D106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>252</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
@@ -3288,7 +3498,9 @@
       <c r="C107" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="D107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>254</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
@@ -3300,7 +3512,9 @@
       <c r="C108" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="D108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>256</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
@@ -3312,7 +3526,9 @@
       <c r="C109" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="D109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>258</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
@@ -3324,7 +3540,9 @@
       <c r="C110" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="D110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>260</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
@@ -3336,7 +3554,9 @@
       <c r="C111" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="D111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>262</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
@@ -3348,7 +3568,9 @@
       <c r="C112" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="D112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>264</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
@@ -3360,7 +3582,9 @@
       <c r="C113" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="D113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>266</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
@@ -3372,7 +3596,9 @@
       <c r="C114" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="D114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>268</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
@@ -3384,7 +3610,9 @@
       <c r="C115" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="D115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>270</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
@@ -3396,7 +3624,9 @@
       <c r="C116" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="D116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>272</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
@@ -3408,7 +3638,9 @@
       <c r="C117" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="D117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>274</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
@@ -3420,7 +3652,9 @@
       <c r="C118" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="D118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>276</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
@@ -3432,7 +3666,9 @@
       <c r="C119" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="D119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>278</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
@@ -3444,7 +3680,9 @@
       <c r="C120" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="D120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>280</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
@@ -3456,7 +3694,9 @@
       <c r="C121" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="D121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>282</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
@@ -3468,7 +3708,9 @@
       <c r="C122" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="D122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>284</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
@@ -3480,7 +3722,9 @@
       <c r="C123" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="D123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>286</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
@@ -3492,7 +3736,9 @@
       <c r="C124" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="D124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>288</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
@@ -3504,7 +3750,9 @@
       <c r="C125" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="D125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>290</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
@@ -3516,7 +3764,9 @@
       <c r="C126" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="D126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>292</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
@@ -3528,7 +3778,9 @@
       <c r="C127" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="D127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>294</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
@@ -3540,7 +3792,9 @@
       <c r="C128" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="D128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>296</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
@@ -3552,7 +3806,9 @@
       <c r="C129" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="D129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>298</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
@@ -3564,7 +3820,9 @@
       <c r="C130" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="D130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>300</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
@@ -3576,7 +3834,9 @@
       <c r="C131" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="D131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>302</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
@@ -3588,7 +3848,9 @@
       <c r="C132" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="D132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>304</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
@@ -3600,7 +3862,9 @@
       <c r="C133" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="D133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>306</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
@@ -3612,7 +3876,9 @@
       <c r="C134" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="D134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>308</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
@@ -3624,7 +3890,9 @@
       <c r="C135" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="D135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>310</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
@@ -3636,7 +3904,9 @@
       <c r="C136" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="D136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>312</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
@@ -3648,7 +3918,9 @@
       <c r="C137" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="D137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>314</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
@@ -3660,7 +3932,9 @@
       <c r="C138" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="D138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>316</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
@@ -3672,7 +3946,9 @@
       <c r="C139" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="D139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>318</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
@@ -3684,7 +3960,9 @@
       <c r="C140" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="D140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>320</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
@@ -3696,7 +3974,9 @@
       <c r="C141" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="D141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>322</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
@@ -3708,7 +3988,9 @@
       <c r="C142" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="D142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>324</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
@@ -3720,7 +4002,9 @@
       <c r="C143" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="D143" s="2"/>
+      <c r="D143" t="s" s="2">
+        <v>326</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
@@ -3732,7 +4016,9 @@
       <c r="C144" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="D144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>328</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
@@ -3744,7 +4030,9 @@
       <c r="C145" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="D145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>330</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
@@ -3756,7 +4044,9 @@
       <c r="C146" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="D146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>332</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
@@ -3768,7 +4058,9 @@
       <c r="C147" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="D147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>334</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
@@ -3780,7 +4072,9 @@
       <c r="C148" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="D148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>336</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
@@ -3792,7 +4086,9 @@
       <c r="C149" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="D149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>338</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
@@ -3804,7 +4100,9 @@
       <c r="C150" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="D150" s="2"/>
+      <c r="D150" t="s" s="2">
+        <v>340</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
@@ -3816,7 +4114,9 @@
       <c r="C151" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="D151" s="2"/>
+      <c r="D151" t="s" s="2">
+        <v>342</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
@@ -3828,7 +4128,9 @@
       <c r="C152" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="D152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>344</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
@@ -3840,7 +4142,9 @@
       <c r="C153" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="D153" s="2"/>
+      <c r="D153" t="s" s="2">
+        <v>346</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
@@ -3852,7 +4156,9 @@
       <c r="C154" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="D154" s="2"/>
+      <c r="D154" t="s" s="2">
+        <v>348</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
@@ -3864,7 +4170,9 @@
       <c r="C155" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="D155" s="2"/>
+      <c r="D155" t="s" s="2">
+        <v>350</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
@@ -3876,7 +4184,9 @@
       <c r="C156" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="D156" s="2"/>
+      <c r="D156" t="s" s="2">
+        <v>352</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
@@ -3888,7 +4198,9 @@
       <c r="C157" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="D157" s="2"/>
+      <c r="D157" t="s" s="2">
+        <v>354</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
@@ -3900,7 +4212,9 @@
       <c r="C158" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="D158" s="2"/>
+      <c r="D158" t="s" s="2">
+        <v>356</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
@@ -3912,7 +4226,9 @@
       <c r="C159" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="D159" s="2"/>
+      <c r="D159" t="s" s="2">
+        <v>358</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
@@ -3924,7 +4240,9 @@
       <c r="C160" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="D160" s="2"/>
+      <c r="D160" t="s" s="2">
+        <v>360</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
@@ -3936,7 +4254,9 @@
       <c r="C161" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="D161" s="2"/>
+      <c r="D161" t="s" s="2">
+        <v>362</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
@@ -3948,7 +4268,9 @@
       <c r="C162" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="D162" s="2"/>
+      <c r="D162" t="s" s="2">
+        <v>364</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
@@ -3960,7 +4282,9 @@
       <c r="C163" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="D163" s="2"/>
+      <c r="D163" t="s" s="2">
+        <v>366</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
@@ -3972,7 +4296,9 @@
       <c r="C164" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="D164" s="2"/>
+      <c r="D164" t="s" s="2">
+        <v>368</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
@@ -3984,7 +4310,9 @@
       <c r="C165" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="D165" s="2"/>
+      <c r="D165" t="s" s="2">
+        <v>370</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
@@ -3996,7 +4324,9 @@
       <c r="C166" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="D166" s="2"/>
+      <c r="D166" t="s" s="2">
+        <v>372</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
@@ -4008,7 +4338,9 @@
       <c r="C167" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="D167" s="2"/>
+      <c r="D167" t="s" s="2">
+        <v>374</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
@@ -4020,7 +4352,9 @@
       <c r="C168" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="D168" s="2"/>
+      <c r="D168" t="s" s="2">
+        <v>376</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
@@ -4032,7 +4366,9 @@
       <c r="C169" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="D169" s="2"/>
+      <c r="D169" t="s" s="2">
+        <v>378</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
@@ -4044,7 +4380,9 @@
       <c r="C170" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="D170" s="2"/>
+      <c r="D170" t="s" s="2">
+        <v>380</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
@@ -4056,7 +4394,9 @@
       <c r="C171" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="D171" s="2"/>
+      <c r="D171" t="s" s="2">
+        <v>382</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
@@ -4068,7 +4408,9 @@
       <c r="C172" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="D172" s="2"/>
+      <c r="D172" t="s" s="2">
+        <v>384</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
@@ -4080,7 +4422,9 @@
       <c r="C173" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="D173" s="2"/>
+      <c r="D173" t="s" s="2">
+        <v>386</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
@@ -4092,7 +4436,9 @@
       <c r="C174" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="D174" s="2"/>
+      <c r="D174" t="s" s="2">
+        <v>388</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
@@ -4104,7 +4450,9 @@
       <c r="C175" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="D175" s="2"/>
+      <c r="D175" t="s" s="2">
+        <v>390</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
@@ -4116,7 +4464,9 @@
       <c r="C176" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="D176" s="2"/>
+      <c r="D176" t="s" s="2">
+        <v>392</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
@@ -4128,7 +4478,9 @@
       <c r="C177" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="D177" s="2"/>
+      <c r="D177" t="s" s="2">
+        <v>394</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
@@ -4140,7 +4492,9 @@
       <c r="C178" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="D178" s="2"/>
+      <c r="D178" t="s" s="2">
+        <v>396</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
@@ -4152,7 +4506,9 @@
       <c r="C179" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="D179" s="2"/>
+      <c r="D179" t="s" s="2">
+        <v>398</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
@@ -4164,7 +4520,9 @@
       <c r="C180" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="D180" s="2"/>
+      <c r="D180" t="s" s="2">
+        <v>400</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
@@ -4176,7 +4534,9 @@
       <c r="C181" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="D181" s="2"/>
+      <c r="D181" t="s" s="2">
+        <v>402</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
@@ -4188,7 +4548,9 @@
       <c r="C182" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="D182" s="2"/>
+      <c r="D182" t="s" s="2">
+        <v>404</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
@@ -4200,7 +4562,9 @@
       <c r="C183" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="D183" s="2"/>
+      <c r="D183" t="s" s="2">
+        <v>406</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
@@ -4212,7 +4576,9 @@
       <c r="C184" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="D184" s="2"/>
+      <c r="D184" t="s" s="2">
+        <v>408</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
@@ -4224,7 +4590,9 @@
       <c r="C185" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="D185" s="2"/>
+      <c r="D185" t="s" s="2">
+        <v>410</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
@@ -4236,7 +4604,9 @@
       <c r="C186" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="D186" s="2"/>
+      <c r="D186" t="s" s="2">
+        <v>412</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
@@ -4248,7 +4618,9 @@
       <c r="C187" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="D187" s="2"/>
+      <c r="D187" t="s" s="2">
+        <v>414</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
@@ -4260,7 +4632,9 @@
       <c r="C188" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="D188" s="2"/>
+      <c r="D188" t="s" s="2">
+        <v>416</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
@@ -4272,7 +4646,9 @@
       <c r="C189" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="D189" s="2"/>
+      <c r="D189" t="s" s="2">
+        <v>418</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
@@ -4284,7 +4660,9 @@
       <c r="C190" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="D190" s="2"/>
+      <c r="D190" t="s" s="2">
+        <v>420</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
@@ -4296,7 +4674,9 @@
       <c r="C191" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="D191" s="2"/>
+      <c r="D191" t="s" s="2">
+        <v>422</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
@@ -4308,7 +4688,9 @@
       <c r="C192" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="D192" s="2"/>
+      <c r="D192" t="s" s="2">
+        <v>424</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
@@ -4320,7 +4702,9 @@
       <c r="C193" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="D193" s="2"/>
+      <c r="D193" t="s" s="2">
+        <v>426</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
@@ -4332,7 +4716,9 @@
       <c r="C194" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="D194" s="2"/>
+      <c r="D194" t="s" s="2">
+        <v>428</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
@@ -4344,7 +4730,9 @@
       <c r="C195" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="D195" s="2"/>
+      <c r="D195" t="s" s="2">
+        <v>430</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
@@ -4356,7 +4744,9 @@
       <c r="C196" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="D196" s="2"/>
+      <c r="D196" t="s" s="2">
+        <v>432</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
@@ -4368,7 +4758,9 @@
       <c r="C197" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="D197" s="2"/>
+      <c r="D197" t="s" s="2">
+        <v>434</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
@@ -4380,7 +4772,9 @@
       <c r="C198" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="D198" s="2"/>
+      <c r="D198" t="s" s="2">
+        <v>436</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
@@ -4392,7 +4786,9 @@
       <c r="C199" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="D199" s="2"/>
+      <c r="D199" t="s" s="2">
+        <v>438</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
@@ -4404,7 +4800,9 @@
       <c r="C200" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="D200" s="2"/>
+      <c r="D200" t="s" s="2">
+        <v>440</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
@@ -4416,7 +4814,9 @@
       <c r="C201" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="D201" s="2"/>
+      <c r="D201" t="s" s="2">
+        <v>442</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
@@ -4428,7 +4828,9 @@
       <c r="C202" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="D202" s="2"/>
+      <c r="D202" t="s" s="2">
+        <v>444</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
@@ -4440,7 +4842,9 @@
       <c r="C203" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="D203" s="2"/>
+      <c r="D203" t="s" s="2">
+        <v>446</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
@@ -4452,7 +4856,9 @@
       <c r="C204" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="D204" s="2"/>
+      <c r="D204" t="s" s="2">
+        <v>448</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
@@ -4464,7 +4870,9 @@
       <c r="C205" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="D205" s="2"/>
+      <c r="D205" t="s" s="2">
+        <v>450</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
@@ -4476,7 +4884,9 @@
       <c r="C206" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="D206" s="2"/>
+      <c r="D206" t="s" s="2">
+        <v>452</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
@@ -4488,7 +4898,9 @@
       <c r="C207" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="D207" s="2"/>
+      <c r="D207" t="s" s="2">
+        <v>454</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
@@ -4500,7 +4912,9 @@
       <c r="C208" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="D208" s="2"/>
+      <c r="D208" t="s" s="2">
+        <v>456</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
@@ -4512,7 +4926,9 @@
       <c r="C209" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="D209" s="2"/>
+      <c r="D209" t="s" s="2">
+        <v>458</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
@@ -4524,7 +4940,9 @@
       <c r="C210" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="D210" s="2"/>
+      <c r="D210" t="s" s="2">
+        <v>460</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
@@ -4536,7 +4954,9 @@
       <c r="C211" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="D211" s="2"/>
+      <c r="D211" t="s" s="2">
+        <v>462</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
@@ -4548,7 +4968,9 @@
       <c r="C212" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="D212" s="2"/>
+      <c r="D212" t="s" s="2">
+        <v>464</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
@@ -4560,7 +4982,9 @@
       <c r="C213" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="D213" s="2"/>
+      <c r="D213" t="s" s="2">
+        <v>466</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
@@ -4572,7 +4996,9 @@
       <c r="C214" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="D214" s="2"/>
+      <c r="D214" t="s" s="2">
+        <v>468</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
@@ -4584,7 +5010,9 @@
       <c r="C215" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="D215" s="2"/>
+      <c r="D215" t="s" s="2">
+        <v>470</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
@@ -4596,7 +5024,9 @@
       <c r="C216" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="D216" s="2"/>
+      <c r="D216" t="s" s="2">
+        <v>472</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
@@ -4608,7 +5038,9 @@
       <c r="C217" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="D217" s="2"/>
+      <c r="D217" t="s" s="2">
+        <v>474</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
@@ -4620,7 +5052,9 @@
       <c r="C218" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="D218" s="2"/>
+      <c r="D218" t="s" s="2">
+        <v>476</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
@@ -4632,7 +5066,9 @@
       <c r="C219" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="D219" s="2"/>
+      <c r="D219" t="s" s="2">
+        <v>478</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
@@ -4644,7 +5080,9 @@
       <c r="C220" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="D220" s="2"/>
+      <c r="D220" t="s" s="2">
+        <v>480</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
@@ -4656,7 +5094,9 @@
       <c r="C221" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="D221" s="2"/>
+      <c r="D221" t="s" s="2">
+        <v>482</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
@@ -4668,7 +5108,9 @@
       <c r="C222" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="D222" s="2"/>
+      <c r="D222" t="s" s="2">
+        <v>484</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
@@ -4680,7 +5122,9 @@
       <c r="C223" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="D223" s="2"/>
+      <c r="D223" t="s" s="2">
+        <v>486</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
@@ -4692,7 +5136,9 @@
       <c r="C224" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="D224" s="2"/>
+      <c r="D224" t="s" s="2">
+        <v>488</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
@@ -4704,7 +5150,9 @@
       <c r="C225" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="D225" s="2"/>
+      <c r="D225" t="s" s="2">
+        <v>490</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
@@ -4716,7 +5164,9 @@
       <c r="C226" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="D226" s="2"/>
+      <c r="D226" t="s" s="2">
+        <v>492</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
@@ -4728,7 +5178,9 @@
       <c r="C227" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="D227" s="2"/>
+      <c r="D227" t="s" s="2">
+        <v>494</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
@@ -4740,7 +5192,9 @@
       <c r="C228" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="D228" s="2"/>
+      <c r="D228" t="s" s="2">
+        <v>496</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
@@ -4752,7 +5206,9 @@
       <c r="C229" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="D229" s="2"/>
+      <c r="D229" t="s" s="2">
+        <v>498</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
@@ -4764,7 +5220,9 @@
       <c r="C230" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="D230" s="2"/>
+      <c r="D230" t="s" s="2">
+        <v>500</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
@@ -4776,7 +5234,9 @@
       <c r="C231" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="D231" s="2"/>
+      <c r="D231" t="s" s="2">
+        <v>502</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
@@ -4788,7 +5248,9 @@
       <c r="C232" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="D232" s="2"/>
+      <c r="D232" t="s" s="2">
+        <v>504</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
@@ -4800,7 +5262,9 @@
       <c r="C233" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="D233" s="2"/>
+      <c r="D233" t="s" s="2">
+        <v>506</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
@@ -4812,7 +5276,9 @@
       <c r="C234" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="D234" s="2"/>
+      <c r="D234" t="s" s="2">
+        <v>508</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
@@ -4824,7 +5290,9 @@
       <c r="C235" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="D235" s="2"/>
+      <c r="D235" t="s" s="2">
+        <v>510</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
@@ -4836,7 +5304,9 @@
       <c r="C236" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="D236" s="2"/>
+      <c r="D236" t="s" s="2">
+        <v>512</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
@@ -4848,7 +5318,9 @@
       <c r="C237" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="D237" s="2"/>
+      <c r="D237" t="s" s="2">
+        <v>514</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
@@ -4860,7 +5332,9 @@
       <c r="C238" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="D238" s="2"/>
+      <c r="D238" t="s" s="2">
+        <v>516</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
@@ -4872,7 +5346,9 @@
       <c r="C239" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="D239" s="2"/>
+      <c r="D239" t="s" s="2">
+        <v>518</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
@@ -4884,7 +5360,9 @@
       <c r="C240" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="D240" s="2"/>
+      <c r="D240" t="s" s="2">
+        <v>520</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
@@ -4896,7 +5374,9 @@
       <c r="C241" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="D241" s="2"/>
+      <c r="D241" t="s" s="2">
+        <v>522</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
@@ -4908,7 +5388,9 @@
       <c r="C242" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="D242" s="2"/>
+      <c r="D242" t="s" s="2">
+        <v>524</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
@@ -4920,7 +5402,9 @@
       <c r="C243" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="D243" s="2"/>
+      <c r="D243" t="s" s="2">
+        <v>526</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
@@ -4932,7 +5416,9 @@
       <c r="C244" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="D244" s="2"/>
+      <c r="D244" t="s" s="2">
+        <v>528</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
@@ -4944,7 +5430,9 @@
       <c r="C245" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="D245" s="2"/>
+      <c r="D245" t="s" s="2">
+        <v>530</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
@@ -4956,7 +5444,9 @@
       <c r="C246" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="D246" s="2"/>
+      <c r="D246" t="s" s="2">
+        <v>532</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
@@ -4968,7 +5458,9 @@
       <c r="C247" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="D247" s="2"/>
+      <c r="D247" t="s" s="2">
+        <v>534</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
@@ -4980,7 +5472,9 @@
       <c r="C248" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="D248" s="2"/>
+      <c r="D248" t="s" s="2">
+        <v>536</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
@@ -4992,7 +5486,9 @@
       <c r="C249" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="D249" s="2"/>
+      <c r="D249" t="s" s="2">
+        <v>538</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
@@ -5004,7 +5500,9 @@
       <c r="C250" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="D250" s="2"/>
+      <c r="D250" t="s" s="2">
+        <v>540</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
@@ -5016,7 +5514,9 @@
       <c r="C251" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="D251" s="2"/>
+      <c r="D251" t="s" s="2">
+        <v>542</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
@@ -5028,7 +5528,9 @@
       <c r="C252" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="D252" s="2"/>
+      <c r="D252" t="s" s="2">
+        <v>544</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
@@ -5040,7 +5542,9 @@
       <c r="C253" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="D253" s="2"/>
+      <c r="D253" t="s" s="2">
+        <v>546</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
@@ -5052,7 +5556,9 @@
       <c r="C254" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="D254" s="2"/>
+      <c r="D254" t="s" s="2">
+        <v>548</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
@@ -5064,7 +5570,9 @@
       <c r="C255" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="D255" s="2"/>
+      <c r="D255" t="s" s="2">
+        <v>550</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
@@ -5076,7 +5584,9 @@
       <c r="C256" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="D256" s="2"/>
+      <c r="D256" t="s" s="2">
+        <v>552</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
@@ -5088,7 +5598,9 @@
       <c r="C257" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="D257" s="2"/>
+      <c r="D257" t="s" s="2">
+        <v>554</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
@@ -5100,7 +5612,9 @@
       <c r="C258" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="D258" s="2"/>
+      <c r="D258" t="s" s="2">
+        <v>554</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
@@ -5112,7 +5626,9 @@
       <c r="C259" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="D259" s="2"/>
+      <c r="D259" t="s" s="2">
+        <v>554</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
